--- a/AI_Guidelines_Master_Git.xlsx
+++ b/AI_Guidelines_Master_Git.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mirconussbaum/Desktop/AI Mapping/ai-map-github/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mirconussbaum/Desktop/AI Mapping/ai_map_28052026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A91412-34A3-9A48-BA62-205B505F50D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5DE2D15-AE1D-3644-8D36-1001DC6CCEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
